--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post FET_HRM-2031-0472/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post FET_HRM-2031-0472/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,26 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad Pos 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.33957</v>
+        <v>17.34113</v>
       </c>
       <c r="D2" t="n">
-        <v>16.97683</v>
+        <v>17.02426</v>
       </c>
       <c r="E2" t="n">
-        <v>17.02223</v>
+        <v>17.14249</v>
       </c>
       <c r="F2" t="n">
-        <v>43.84172</v>
+        <v>43.28936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05235</v>
+        <v>0.05071</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85794</v>
+        <v>1.91038</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.27528</v>
+        <v>17.70421</v>
       </c>
       <c r="D3" t="n">
-        <v>17.17546</v>
+        <v>16.80847</v>
       </c>
       <c r="E3" t="n">
-        <v>16.96369</v>
+        <v>17.39821</v>
       </c>
       <c r="F3" t="n">
-        <v>43.41054</v>
+        <v>44.11026</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0527</v>
+        <v>0.05042</v>
       </c>
       <c r="H3" t="n">
-        <v>1.88203</v>
+        <v>1.90368</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.58058</v>
+        <v>17.46082</v>
       </c>
       <c r="D4" t="n">
-        <v>16.92808</v>
+        <v>17.10625</v>
       </c>
       <c r="E4" t="n">
-        <v>17.08138</v>
+        <v>17.24969</v>
       </c>
       <c r="F4" t="n">
-        <v>43.1493</v>
+        <v>44.34662</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05269</v>
+        <v>0.05163</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83456</v>
+        <v>1.91307</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.51554</v>
+        <v>17.55314</v>
       </c>
       <c r="D5" t="n">
-        <v>17.10289</v>
+        <v>16.83994</v>
       </c>
       <c r="E5" t="n">
-        <v>17.25836</v>
+        <v>17.09306</v>
       </c>
       <c r="F5" t="n">
-        <v>44.37153</v>
+        <v>44.93257</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05205</v>
+        <v>0.05189</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8635</v>
+        <v>1.89132</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.35232</v>
+        <v>17.20144</v>
       </c>
       <c r="D6" t="n">
-        <v>16.66214</v>
+        <v>16.93201</v>
       </c>
       <c r="E6" t="n">
-        <v>17.35252</v>
+        <v>17.02101</v>
       </c>
       <c r="F6" t="n">
-        <v>43.75019</v>
+        <v>43.47803</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05349</v>
+        <v>0.05147</v>
       </c>
       <c r="H6" t="n">
-        <v>1.87679</v>
+        <v>1.86408</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.11358</v>
+        <v>17.61047</v>
       </c>
       <c r="D7" t="n">
-        <v>16.91719</v>
+        <v>16.98945</v>
       </c>
       <c r="E7" t="n">
-        <v>16.88262</v>
+        <v>17.43193</v>
       </c>
       <c r="F7" t="n">
-        <v>43.73102</v>
+        <v>43.76242</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0529</v>
+        <v>0.05174</v>
       </c>
       <c r="H7" t="n">
-        <v>1.88158</v>
+        <v>1.90675</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.82141</v>
+        <v>17.3098</v>
       </c>
       <c r="D8" t="n">
-        <v>16.81247</v>
+        <v>17.03147</v>
       </c>
       <c r="E8" t="n">
-        <v>17.22505</v>
+        <v>17.29593</v>
       </c>
       <c r="F8" t="n">
-        <v>44.88883</v>
+        <v>43.41321</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05187</v>
+        <v>0.05078</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8704</v>
+        <v>1.85928</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.4353</v>
+        <v>17.2819</v>
       </c>
       <c r="D9" t="n">
-        <v>17.44483</v>
+        <v>16.98991</v>
       </c>
       <c r="E9" t="n">
-        <v>17.27913</v>
+        <v>17.21736</v>
       </c>
       <c r="F9" t="n">
-        <v>42.74671</v>
+        <v>44.45767</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0519</v>
+        <v>0.05102</v>
       </c>
       <c r="H9" t="n">
-        <v>1.88396</v>
+        <v>1.85227</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.50437</v>
+        <v>17.62956</v>
       </c>
       <c r="D10" t="n">
-        <v>17.21127</v>
+        <v>17.01099</v>
       </c>
       <c r="E10" t="n">
-        <v>17.1075</v>
+        <v>17.32141</v>
       </c>
       <c r="F10" t="n">
-        <v>43.69246</v>
+        <v>43.97548</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05295</v>
+        <v>0.05267</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83397</v>
+        <v>1.88918</v>
       </c>
     </row>
     <row r="11">
@@ -718,26 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad Pos 2</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.38278</v>
+        <v>17.39398</v>
       </c>
       <c r="D12" t="n">
-        <v>16.98576</v>
+        <v>16.9987</v>
       </c>
       <c r="E12" t="n">
-        <v>17.30773</v>
+        <v>17.28731</v>
       </c>
       <c r="F12" t="n">
-        <v>43.90905</v>
+        <v>43.11444</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05218</v>
+        <v>0.05269</v>
       </c>
       <c r="H12" t="n">
-        <v>1.87539</v>
+        <v>1.89777</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.65173</v>
+        <v>17.47658</v>
       </c>
       <c r="D13" t="n">
-        <v>17.7426</v>
+        <v>16.81195</v>
       </c>
       <c r="E13" t="n">
-        <v>17.10976</v>
+        <v>17.00412</v>
       </c>
       <c r="F13" t="n">
-        <v>42.92898</v>
+        <v>43.94918</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05292</v>
+        <v>0.05152</v>
       </c>
       <c r="H13" t="n">
-        <v>1.87265</v>
+        <v>1.87413</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.31583</v>
+        <v>17.15009</v>
       </c>
       <c r="D14" t="n">
-        <v>17.11441</v>
+        <v>16.99823</v>
       </c>
       <c r="E14" t="n">
-        <v>16.95419</v>
+        <v>17.08182</v>
       </c>
       <c r="F14" t="n">
-        <v>43.54584</v>
+        <v>43.502</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05207</v>
+        <v>0.05243</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8985</v>
+        <v>1.88396</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.21227</v>
+        <v>17.31098</v>
       </c>
       <c r="D15" t="n">
-        <v>16.90455</v>
+        <v>17.03267</v>
       </c>
       <c r="E15" t="n">
-        <v>17.38719</v>
+        <v>17.07176</v>
       </c>
       <c r="F15" t="n">
-        <v>43.33641</v>
+        <v>43.80111</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05138</v>
+        <v>0.05207</v>
       </c>
       <c r="H15" t="n">
-        <v>1.84841</v>
+        <v>1.90283</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.23732</v>
+        <v>17.0914</v>
       </c>
       <c r="D16" t="n">
-        <v>17.01093</v>
+        <v>16.94704</v>
       </c>
       <c r="E16" t="n">
-        <v>16.99503</v>
+        <v>16.99121</v>
       </c>
       <c r="F16" t="n">
-        <v>44.39024</v>
+        <v>44.46943</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05132</v>
+        <v>0.05278</v>
       </c>
       <c r="H16" t="n">
-        <v>1.89103</v>
+        <v>1.87403</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.63857</v>
+        <v>17.1985</v>
       </c>
       <c r="D17" t="n">
-        <v>17.27429</v>
+        <v>16.73676</v>
       </c>
       <c r="E17" t="n">
-        <v>16.9555</v>
+        <v>17.16988</v>
       </c>
       <c r="F17" t="n">
-        <v>43.39928</v>
+        <v>43.37473</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05195</v>
+        <v>0.05274</v>
       </c>
       <c r="H17" t="n">
-        <v>1.87462</v>
+        <v>1.88303</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.62669</v>
+        <v>17.44405</v>
       </c>
       <c r="D18" t="n">
-        <v>16.86282</v>
+        <v>17.10186</v>
       </c>
       <c r="E18" t="n">
-        <v>17.27426</v>
+        <v>17.38005</v>
       </c>
       <c r="F18" t="n">
-        <v>44.38329</v>
+        <v>43.77087</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05227</v>
+        <v>0.05208</v>
       </c>
       <c r="H18" t="n">
-        <v>1.89222</v>
+        <v>1.89211</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.97869</v>
+        <v>17.63504</v>
       </c>
       <c r="D19" t="n">
-        <v>17.05665</v>
+        <v>16.96241</v>
       </c>
       <c r="E19" t="n">
-        <v>17.14383</v>
+        <v>17.00838</v>
       </c>
       <c r="F19" t="n">
-        <v>43.67331</v>
+        <v>43.47573</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05266</v>
+        <v>0.05138</v>
       </c>
       <c r="H19" t="n">
-        <v>1.91179</v>
+        <v>1.87197</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.44718</v>
+        <v>17.26945</v>
       </c>
       <c r="D20" t="n">
-        <v>17.08911</v>
+        <v>17.04648</v>
       </c>
       <c r="E20" t="n">
-        <v>17.25923</v>
+        <v>17.1469</v>
       </c>
       <c r="F20" t="n">
-        <v>44.59035</v>
+        <v>42.92757</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05165</v>
+        <v>0.05209</v>
       </c>
       <c r="H20" t="n">
-        <v>1.90035</v>
+        <v>1.91149</v>
       </c>
     </row>
     <row r="21">
@@ -970,20 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SR Pad Pos 1</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.40966</v>
+        <v>16.20739</v>
       </c>
       <c r="D22" t="n">
-        <v>15.94177</v>
+        <v>16.14423</v>
       </c>
       <c r="E22" t="n">
-        <v>15.8691</v>
+        <v>16.18446</v>
       </c>
       <c r="F22" t="n">
-        <v>261.91173</v>
+        <v>262.11854</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.0358</v>
+        <v>16.4481</v>
       </c>
       <c r="D23" t="n">
-        <v>15.9965</v>
+        <v>16.22574</v>
       </c>
       <c r="E23" t="n">
-        <v>16.15529</v>
+        <v>16.34355</v>
       </c>
       <c r="F23" t="n">
-        <v>262.98195</v>
+        <v>264.73964</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.84155</v>
+        <v>16.07131</v>
       </c>
       <c r="D24" t="n">
-        <v>16.16657</v>
+        <v>15.94261</v>
       </c>
       <c r="E24" t="n">
-        <v>15.92457</v>
+        <v>16.04136</v>
       </c>
       <c r="F24" t="n">
-        <v>266.11233</v>
+        <v>267.47337</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.70787</v>
+        <v>16.41653</v>
       </c>
       <c r="D25" t="n">
-        <v>16.15411</v>
+        <v>15.89103</v>
       </c>
       <c r="E25" t="n">
-        <v>16.33769</v>
+        <v>16.03416</v>
       </c>
       <c r="F25" t="n">
-        <v>264.71851</v>
+        <v>266.17966</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.52247</v>
+        <v>16.23809</v>
       </c>
       <c r="D26" t="n">
-        <v>15.94562</v>
+        <v>15.74821</v>
       </c>
       <c r="E26" t="n">
-        <v>16.10111</v>
+        <v>15.86732</v>
       </c>
       <c r="F26" t="n">
-        <v>261.16113</v>
+        <v>262.92437</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.16176</v>
+        <v>16.1189</v>
       </c>
       <c r="D27" t="n">
-        <v>15.84104</v>
+        <v>15.96021</v>
       </c>
       <c r="E27" t="n">
-        <v>15.86713</v>
+        <v>16.08356</v>
       </c>
       <c r="F27" t="n">
-        <v>266.67761</v>
+        <v>257.39878</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.01404</v>
+        <v>16.44808</v>
       </c>
       <c r="D28" t="n">
-        <v>15.77617</v>
+        <v>16.1187</v>
       </c>
       <c r="E28" t="n">
-        <v>16.1913</v>
+        <v>16.14293</v>
       </c>
       <c r="F28" t="n">
-        <v>263.76426</v>
+        <v>260.98245</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.28497</v>
+        <v>16.27371</v>
       </c>
       <c r="D29" t="n">
-        <v>16.04365</v>
+        <v>16.21101</v>
       </c>
       <c r="E29" t="n">
-        <v>16.06208</v>
+        <v>16.23583</v>
       </c>
       <c r="F29" t="n">
-        <v>265.11623</v>
+        <v>265.41418</v>
       </c>
     </row>
     <row r="30">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.06422</v>
+        <v>16.23909</v>
       </c>
       <c r="D30" t="n">
-        <v>15.9388</v>
+        <v>15.84961</v>
       </c>
       <c r="E30" t="n">
-        <v>16.16717</v>
+        <v>16.21582</v>
       </c>
       <c r="F30" t="n">
-        <v>266.20667</v>
+        <v>263.98818</v>
       </c>
     </row>
     <row r="31">
@@ -1173,23 +1173,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trace Pos 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17.24777</v>
+        <v>17.06817</v>
       </c>
       <c r="D32" t="n">
-        <v>16.32288</v>
+        <v>16.5431</v>
       </c>
       <c r="E32" t="n">
-        <v>17.02436</v>
+        <v>16.56228</v>
       </c>
       <c r="F32" t="n">
-        <v>22.28161</v>
+        <v>22.6576</v>
       </c>
       <c r="G32" t="n">
-        <v>35.70699</v>
+        <v>34.40216</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17.17265</v>
+        <v>17.30989</v>
       </c>
       <c r="D33" t="n">
-        <v>16.69776</v>
+        <v>16.31005</v>
       </c>
       <c r="E33" t="n">
-        <v>16.73825</v>
+        <v>16.62794</v>
       </c>
       <c r="F33" t="n">
-        <v>21.98467</v>
+        <v>22.23368</v>
       </c>
       <c r="G33" t="n">
-        <v>35.28669</v>
+        <v>34.29879</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>17.22255</v>
+        <v>17.39261</v>
       </c>
       <c r="D34" t="n">
-        <v>16.60829</v>
+        <v>16.10395</v>
       </c>
       <c r="E34" t="n">
-        <v>16.70182</v>
+        <v>17.15153</v>
       </c>
       <c r="F34" t="n">
-        <v>22.58636</v>
+        <v>22.31818</v>
       </c>
       <c r="G34" t="n">
-        <v>35.26419</v>
+        <v>35.4245</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17.22938</v>
+        <v>16.96579</v>
       </c>
       <c r="D35" t="n">
-        <v>16.47326</v>
+        <v>16.7877</v>
       </c>
       <c r="E35" t="n">
-        <v>17.10166</v>
+        <v>16.91567</v>
       </c>
       <c r="F35" t="n">
-        <v>22.55518</v>
+        <v>21.7315</v>
       </c>
       <c r="G35" t="n">
-        <v>35.46807</v>
+        <v>34.65801</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16.77978</v>
+        <v>17.3177</v>
       </c>
       <c r="D36" t="n">
-        <v>16.34166</v>
+        <v>16.3318</v>
       </c>
       <c r="E36" t="n">
-        <v>16.98142</v>
+        <v>16.52169</v>
       </c>
       <c r="F36" t="n">
-        <v>22.24074</v>
+        <v>22.49247</v>
       </c>
       <c r="G36" t="n">
-        <v>35.2061</v>
+        <v>34.89753</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>17.06558</v>
+        <v>17.1607</v>
       </c>
       <c r="D37" t="n">
-        <v>16.56186</v>
+        <v>16.2067</v>
       </c>
       <c r="E37" t="n">
-        <v>16.72655</v>
+        <v>16.88765</v>
       </c>
       <c r="F37" t="n">
-        <v>21.87646</v>
+        <v>22.90266</v>
       </c>
       <c r="G37" t="n">
-        <v>34.90834</v>
+        <v>35.01644</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>16.90877</v>
+        <v>17.06083</v>
       </c>
       <c r="D38" t="n">
-        <v>16.41647</v>
+        <v>16.30705</v>
       </c>
       <c r="E38" t="n">
-        <v>16.98739</v>
+        <v>16.82533</v>
       </c>
       <c r="F38" t="n">
-        <v>22.47528</v>
+        <v>22.09505</v>
       </c>
       <c r="G38" t="n">
-        <v>36.2659</v>
+        <v>35.42081</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>17.71593</v>
+        <v>17.16666</v>
       </c>
       <c r="D39" t="n">
-        <v>16.59471</v>
+        <v>16.86967</v>
       </c>
       <c r="E39" t="n">
-        <v>16.74992</v>
+        <v>16.89023</v>
       </c>
       <c r="F39" t="n">
-        <v>22.18901</v>
+        <v>21.97892</v>
       </c>
       <c r="G39" t="n">
-        <v>35.50834</v>
+        <v>35.16894</v>
       </c>
     </row>
     <row r="40">
@@ -1353,30 +1353,45 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17.29237</v>
+        <v>17.12304</v>
       </c>
       <c r="D40" t="n">
-        <v>16.44876</v>
+        <v>16.38046</v>
       </c>
       <c r="E40" t="n">
-        <v>17.19085</v>
+        <v>17.03117</v>
       </c>
       <c r="F40" t="n">
-        <v>23.07863</v>
+        <v>22.55603</v>
       </c>
       <c r="G40" t="n">
-        <v>35.30862</v>
+        <v>35.15647</v>
       </c>
     </row>
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -1388,14 +1403,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Via Pos 1</t>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.61841</v>
+        <v>17.26887</v>
       </c>
       <c r="D42" t="n">
-        <v>1.15344</v>
+        <v>16.42043</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.6315</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.3624</v>
+      </c>
+      <c r="G42" t="n">
+        <v>35.33472</v>
       </c>
     </row>
     <row r="43">
@@ -1405,10 +1429,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.62091</v>
+        <v>17.34883</v>
       </c>
       <c r="D43" t="n">
-        <v>1.14229</v>
+        <v>16.48429</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.76096</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.19121</v>
+      </c>
+      <c r="G43" t="n">
+        <v>35.78421</v>
       </c>
     </row>
     <row r="44">
@@ -1418,10 +1451,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.6233</v>
+        <v>17.24711</v>
       </c>
       <c r="D44" t="n">
-        <v>1.16183</v>
+        <v>16.73654</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.94404</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22.03544</v>
+      </c>
+      <c r="G44" t="n">
+        <v>35.04884</v>
       </c>
     </row>
     <row r="45">
@@ -1431,10 +1473,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.61283</v>
+        <v>17.3526</v>
       </c>
       <c r="D45" t="n">
-        <v>1.14933</v>
+        <v>16.71342</v>
+      </c>
+      <c r="E45" t="n">
+        <v>17.12727</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22.08346</v>
+      </c>
+      <c r="G45" t="n">
+        <v>35.14293</v>
       </c>
     </row>
     <row r="46">
@@ -1444,10 +1495,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.62382</v>
+        <v>17.12027</v>
       </c>
       <c r="D46" t="n">
-        <v>1.14326</v>
+        <v>16.27799</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.88493</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.76758</v>
+      </c>
+      <c r="G46" t="n">
+        <v>35.18186</v>
       </c>
     </row>
     <row r="47">
@@ -1457,10 +1517,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.62103</v>
+        <v>17.04169</v>
       </c>
       <c r="D47" t="n">
-        <v>1.15099</v>
+        <v>16.70596</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22.31519</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.40105</v>
       </c>
     </row>
     <row r="48">
@@ -1470,10 +1539,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.6151</v>
+        <v>17.00185</v>
       </c>
       <c r="D48" t="n">
-        <v>1.16127</v>
+        <v>16.22657</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.96666</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.72636</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.91056</v>
       </c>
     </row>
     <row r="49">
@@ -1483,10 +1561,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.6301600000000001</v>
+        <v>17.22499</v>
       </c>
       <c r="D49" t="n">
-        <v>1.14663</v>
+        <v>16.3617</v>
+      </c>
+      <c r="E49" t="n">
+        <v>17.1642</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22.34464</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.79383</v>
       </c>
     </row>
     <row r="50">
@@ -1496,31 +1583,30 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.6206700000000001</v>
+        <v>17.21856</v>
       </c>
       <c r="D50" t="n">
-        <v>1.1557</v>
+        <v>16.82724</v>
+      </c>
+      <c r="E50" t="n">
+        <v>17.02806</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.55414</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.5511</v>
       </c>
     </row>
     <row r="51">
       <c r="C51" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Radius</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -1532,20 +1618,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Landing Pad 1</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>17.40348</v>
+        <v>0.63125</v>
       </c>
       <c r="D52" t="n">
-        <v>17.27129</v>
-      </c>
-      <c r="E52" t="n">
-        <v>17.14933</v>
-      </c>
-      <c r="F52" t="n">
-        <v>44.20667</v>
+        <v>1.147</v>
       </c>
     </row>
     <row r="53">
@@ -1555,16 +1635,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>16.85574</v>
+        <v>0.62147</v>
       </c>
       <c r="D53" t="n">
-        <v>17.39046</v>
-      </c>
-      <c r="E53" t="n">
-        <v>16.9262</v>
-      </c>
-      <c r="F53" t="n">
-        <v>43.37743</v>
+        <v>1.15455</v>
       </c>
     </row>
     <row r="54">
@@ -1574,16 +1648,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>17.47743</v>
+        <v>0.62995</v>
       </c>
       <c r="D54" t="n">
-        <v>17.17925</v>
-      </c>
-      <c r="E54" t="n">
-        <v>17.21426</v>
-      </c>
-      <c r="F54" t="n">
-        <v>43.49717</v>
+        <v>1.13201</v>
       </c>
     </row>
     <row r="55">
@@ -1593,16 +1661,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>17.02823</v>
+        <v>0.61999</v>
       </c>
       <c r="D55" t="n">
-        <v>17.30815</v>
-      </c>
-      <c r="E55" t="n">
-        <v>17.29247</v>
-      </c>
-      <c r="F55" t="n">
-        <v>43.6528</v>
+        <v>1.13083</v>
       </c>
     </row>
     <row r="56">
@@ -1612,16 +1674,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>17.34322</v>
+        <v>0.60893</v>
       </c>
       <c r="D56" t="n">
-        <v>16.88096</v>
-      </c>
-      <c r="E56" t="n">
-        <v>17.31692</v>
-      </c>
-      <c r="F56" t="n">
-        <v>43.33547</v>
+        <v>1.1215</v>
       </c>
     </row>
     <row r="57">
@@ -1631,16 +1687,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>17.36684</v>
+        <v>0.62448</v>
       </c>
       <c r="D57" t="n">
-        <v>16.99231</v>
-      </c>
-      <c r="E57" t="n">
-        <v>16.88984</v>
-      </c>
-      <c r="F57" t="n">
-        <v>43.61536</v>
+        <v>1.15746</v>
       </c>
     </row>
     <row r="58">
@@ -1650,16 +1700,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>17.11213</v>
+        <v>0.63426</v>
       </c>
       <c r="D58" t="n">
-        <v>16.75835</v>
-      </c>
-      <c r="E58" t="n">
-        <v>17.19478</v>
-      </c>
-      <c r="F58" t="n">
-        <v>43.68497</v>
+        <v>1.15612</v>
       </c>
     </row>
     <row r="59">
@@ -1669,16 +1713,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>16.94984</v>
+        <v>0.62678</v>
       </c>
       <c r="D59" t="n">
-        <v>17.06917</v>
-      </c>
-      <c r="E59" t="n">
-        <v>17.3156</v>
-      </c>
-      <c r="F59" t="n">
-        <v>42.38504</v>
+        <v>1.14347</v>
       </c>
     </row>
     <row r="60">
@@ -1688,16 +1726,144 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>17.29225</v>
+        <v>0.60803</v>
       </c>
       <c r="D60" t="n">
-        <v>17.39102</v>
-      </c>
-      <c r="E60" t="n">
-        <v>17.06781</v>
-      </c>
-      <c r="F60" t="n">
-        <v>44.29938</v>
+        <v>1.14351</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.62187</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.12787</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.6363</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.15404</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.64093</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.14505</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.63424</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.1483</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.62539</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.13183</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.62653</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.14141</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.62447</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.14428</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.63012</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.15894</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.62854</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.12974</v>
       </c>
     </row>
   </sheetData>
